--- a/Assets/WorkSpace/shishido/ExcelData/Item/WeaponsData.xlsx
+++ b/Assets/WorkSpace/shishido/ExcelData/Item/WeaponsData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3.TMIC-GAME1-025\Desktop\卒業制作\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3.TMIC-GAME1-025\Desktop\UnityProject\1v1_FFA\Assets\WorkSpace\shishido\ExcelData\Item\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3827E14-DEAA-4FB8-9C92-7F1C100D93A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25665316-8DC7-48CB-AD48-5036E624E215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5490" yWindow="2475" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3345" yWindow="810" windowWidth="21600" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Weapons" sheetId="1" r:id="rId1"/>
@@ -776,11 +776,11 @@
         <v>3</v>
       </c>
       <c r="G2" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H2" s="8" t="str">
         <f>VLOOKUP(G2,reference!D:E,2,FALSE)</f>
-        <v>BigAmmo</v>
+        <v>MiddleAmmo</v>
       </c>
       <c r="I2" s="7">
         <v>30</v>
@@ -950,11 +950,11 @@
         <v>1.5</v>
       </c>
       <c r="G5" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="8" t="str">
         <f>VLOOKUP(G5,reference!D:E,2,FALSE)</f>
-        <v>MiddleAmmo</v>
+        <v>SmallAmmo</v>
       </c>
       <c r="I5" s="11">
         <v>30</v>
